--- a/final/688775_影石创新_三表抽取.xlsx
+++ b/final/688775_影石创新_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +454,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -478,6 +484,11 @@
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -501,6 +512,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>2015 年 7 月 9 日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本 1,000.00 万元。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -515,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,10 +585,15 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -601,10 +622,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -633,10 +659,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -665,10 +696,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -697,10 +733,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -729,10 +770,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -761,10 +807,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -793,10 +844,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -825,10 +881,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -857,10 +918,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -889,10 +955,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -921,10 +992,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -953,10 +1029,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -985,10 +1066,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1017,10 +1103,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1049,10 +1140,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1081,10 +1177,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1113,10 +1214,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1145,10 +1251,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1177,10 +1288,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1209,10 +1325,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1241,10 +1362,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1273,10 +1399,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1305,10 +1436,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1337,10 +1473,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1369,10 +1510,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1401,10 +1547,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1433,10 +1584,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1467,10 +1623,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1501,10 +1662,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1535,10 +1701,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1569,10 +1740,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1603,10 +1779,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1637,10 +1818,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1671,10 +1857,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1705,10 +1896,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1739,10 +1935,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1773,10 +1974,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1807,10 +2013,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1841,10 +2052,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1875,10 +2091,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1909,10 +2130,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1943,10 +2169,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1977,10 +2208,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2011,10 +2247,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2045,10 +2286,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2079,10 +2325,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2113,10 +2364,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2147,10 +2403,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2181,10 +2442,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2215,10 +2481,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2249,10 +2520,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2283,10 +2559,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2317,10 +2598,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2351,10 +2637,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2383,10 +2674,15 @@
           <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2415,10 +2711,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2447,10 +2748,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2479,10 +2785,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2511,10 +2822,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2543,10 +2859,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2575,10 +2896,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2607,10 +2933,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2639,10 +2970,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2671,10 +3007,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2703,10 +3044,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2735,10 +3081,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2767,10 +3118,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2799,10 +3155,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2831,10 +3192,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2863,10 +3229,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2895,10 +3266,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2927,10 +3303,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2959,10 +3340,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2991,10 +3377,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3023,10 +3414,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3055,10 +3451,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3087,10 +3488,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3119,10 +3525,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3151,10 +3562,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3183,10 +3599,15 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3215,6 +3636,11 @@
           <t>Markdown表格: 1、2023年3月，股份公司第一次股权转让 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3247,6 +3673,11 @@
           <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3279,6 +3710,11 @@
           <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3311,6 +3747,11 @@
           <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3343,6 +3784,11 @@
           <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3375,6 +3821,11 @@
           <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3407,6 +3858,11 @@
           <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3439,6 +3895,11 @@
           <t>Markdown表格: （一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3471,6 +3932,11 @@
           <t>Markdown表格: 1、EARN ACE | 2、QM101, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3503,6 +3969,1466 @@
           <t>Markdown表格: 1、EARN ACE | 2、QM101, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>99</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>EARN ACE</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>4796.6179</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>13.3239</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东EARN ACE持有4796.6179万股，持股比例13.3239%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>99</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>QM101</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>3384.0413</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>9.4001</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东QM101持有3384.0413万股，持股比例9.4001%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>99</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>香港迅雷</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>3143.7542</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>8.732699999999999</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东香港迅雷持有3143.7542万股，持股比例8.7327%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>99</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>岚沣管理</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1464.0237</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>4.0667</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东岚沣管理持有1464.0237万股，持股比例4.0667%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>99</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>华金同达</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1436.7094</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>3.9909</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东华金同达持有1436.7094万股，持股比例3.9909%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>99</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>厦门富凯</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1332.1116</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>3.7003</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东厦门富凯持有1332.1116万股，持股比例3.7003%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>99</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>澜烽管理</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1171.2193</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>3.2534</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东澜烽管理持有1171.2193万股，持股比例3.2534%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>99</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>伊敦传媒</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>976.4985</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>2.7125</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东伊敦传媒持有976.4985万股，持股比例2.7125%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>领誉基石</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>960.1358</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东领誉基石持有960.1358万股，持股比例2.667%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>中证投资</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>911.2616</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>2.5313</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东中证投资持有911.2616万股，持股比例2.5313%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>金石智娱</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>911.2486</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>2.5312</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东金石智娱持有911.2486万股，持股比例2.5312%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>芜湖旷沄</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>638.5374</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>1.7737</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东芜湖旷沄持有638.5374万股，持股比例1.7737%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>朗玛六号</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>600.5396</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>1.6682</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛六号持有600.5396万股，持股比例1.6682%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>99</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>天正投资</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>584.9989</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东天正投资持有584.9989万股，持股比例1.625%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>99</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>朗玛五号</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>540.4859</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>1.5013</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛五号持有540.4859万股，持股比例1.5013%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>汇智同裕</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>478.6264</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>1.3295</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东汇智同裕持有478.6264万股，持股比例1.3295%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>99</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>深圳麦高</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>468.0393</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="n">
+        <v>1.3001</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东深圳麦高持有468.0393万股，持股比例1.3001%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>99</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>朗玛九号</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>455.3182</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>1.2648</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛九号持有455.3182万股，持股比例1.2648%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>99</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>朗玛十四号</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>224.9975</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东朗玛十四号持有224.9975万股，持股比例0.625%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>99</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>利得鑫投</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>216.0001</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东利得鑫投持有216.0001万股，持股比例0.6%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>99</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>华金创盈</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>157.4973</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东华金创盈持有157.4973万股，持股比例0.4375%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>99</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>岚烽管理</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>145.8319</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东岚烽管理持有145.8319万股，持股比例0.4051%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>99</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>威明投资</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>89.99679999999999</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东威明投资持有89.9968万股，持股比例0.25%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>99</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>山东龙兴（SS）</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>70.32680000000001</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东山东龙兴（SS）持有70.3268万股，持股比例0.1954%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>99</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>知盛投资</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>63.6367</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>影石创新首次公开发行股票，发行前股东知盛投资持有63.6367万股，持股比例0.1768%（招股书第99页）</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>检查项</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>公司代码</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验条目</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PDF披露值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>计算值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>差异</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差异率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>是否在容差范围内</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>原文证据</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>股权结构存量</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>688775</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>影石创新 三表抽取</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>文件包含3个sheet</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>688775</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>subscription=2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>transfer=1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>688775</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>各时点持股比例合计</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>570.0624</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>115条快照,比例合计570.06</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>全部时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>688775</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立 (26名股东)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.0000%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1、2023年3月，股份公司第一次股权转让 | 股份公司设立</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>688775</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>发行前（第99页） (25名股东)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>70.0624%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>29.9376%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>合计70.06%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>发行前（第99页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>688775</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>设立时 | 股份公司设立 (54名股东)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>200.0000%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>合计200.00%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>688775</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况 (7名股东)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.0000%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>（一）控股股东及一致行动人、实际控制人的基本情况 | 1、控股股东的基本情况</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
